--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-10-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T00:00:00+00:00</t>
+    <t>2026-10-01T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41264</t>
+    <t>41320</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-bdpm (use: secondary, )</t>
+    <t>https://smt.esante.gouv.fr/#terminologie-bdpm (use: secondary)</t>
   </si>
   <si>
     <t>Version</t>
